--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F347A10A-E364-486D-A617-D4D567BC8BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE1FF89-6A1F-4602-9C25-3ACB27EC77C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="270">
   <si>
     <t>Image</t>
   </si>
@@ -599,33 +599,6 @@
   </si>
   <si>
     <t>Bois polychrome doré</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6c/Tilman_Riemenschneider_Magdalena_BNM_img01.jpg/1280px-Tilman_Riemenschneider_Magdalena_BNM_img01.jpg</t>
-  </si>
-  <si>
-    <t>Tilman</t>
-  </si>
-  <si>
-    <t>RIEMENSCHNEIDER</t>
-  </si>
-  <si>
-    <t>1531</t>
-  </si>
-  <si>
-    <t>1490-1492</t>
-  </si>
-  <si>
-    <t>Munich</t>
-  </si>
-  <si>
-    <t>Bayerisches Nationalmuseum</t>
-  </si>
-  <si>
-    <t>"Retable de Sainte-Madeleine (Münnerstadt Altar)"</t>
-  </si>
-  <si>
-    <t>Bois polychrome</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Francesco_di_giorgio_martini%2C_san_cristoforo%2C_1488-90%2C_da_s._agostino_a_siena.JPG/1280px-Francesco_di_giorgio_martini%2C_san_cristoforo%2C_1488-90%2C_da_s._agostino_a_siena.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
@@ -1238,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T32"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1608,7 +1581,7 @@
         <v>143</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>78</v>
@@ -1791,10 +1764,10 @@
         <v>112</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>113</v>
@@ -2255,15 +2228,15 @@
         <v>193</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>196</v>
@@ -2290,7 +2263,7 @@
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3" t="s">
-        <v>159</v>
+        <v>30</v>
       </c>
       <c r="T22" s="3">
         <v>1</v>
@@ -2301,42 +2274,38 @@
         <v>202</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>50</v>
+        <v>203</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
       <c r="O23" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3" t="s">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="T23" s="3">
         <v>1</v>
@@ -2354,31 +2323,35 @@
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="H24" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>215</v>
+        <v>46</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="3" t="s">
-        <v>218</v>
+        <v>29</v>
       </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3" t="s">
-        <v>219</v>
+        <v>30</v>
       </c>
       <c r="T24" s="3">
         <v>1</v>
@@ -2386,34 +2359,32 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>35</v>
+        <v>196</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>46</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
@@ -2432,32 +2403,34 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
@@ -2476,34 +2449,34 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>234</v>
+        <v>105</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
@@ -2522,34 +2495,34 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="I28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>245</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
@@ -2568,39 +2541,37 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>88</v>
+        <v>248</v>
       </c>
       <c r="G29" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
       <c r="O29" s="3" t="s">
-        <v>29</v>
+        <v>252</v>
       </c>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
@@ -2614,26 +2585,28 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="H30" s="3" t="s">
+      <c r="I30" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
         <v>259</v>
       </c>
@@ -2644,7 +2617,7 @@
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
       <c r="O30" s="3" t="s">
-        <v>261</v>
+        <v>111</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
@@ -2658,39 +2631,39 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>234</v>
+        <v>105</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>263</v>
+        <v>127</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>264</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
       <c r="O31" s="3" t="s">
-        <v>111</v>
+        <v>266</v>
       </c>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
@@ -2702,52 +2675,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="K32" s="3"/>
-      <c r="L32" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T32" s="3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE1FF89-6A1F-4602-9C25-3ACB27EC77C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69B8534-C52B-4152-9FD4-3B543FE5AECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="262">
   <si>
     <t>Image</t>
   </si>
@@ -229,9 +229,6 @@
     <t>néerlandaise</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Benedetto_da_maiano%2C_pulpito_di_s._croce_08.JPG/1280px-Benedetto_da_maiano%2C_pulpito_di_s._croce_08.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Benedetto</t>
   </si>
   <si>
@@ -253,27 +250,6 @@
     <t>"Chaire de Santa Croce"</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/Altare_maggiore_del_duomo_di_siena_02.JPG/1280px-Altare_maggiore_del_duomo_di_siena_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>VECCHIETTA</t>
-  </si>
-  <si>
-    <t>1410</t>
-  </si>
-  <si>
-    <t>1480</t>
-  </si>
-  <si>
-    <t>1467-1472</t>
-  </si>
-  <si>
-    <t>Cathédrale de Sienne</t>
-  </si>
-  <si>
-    <t>"Ciboire en bronze du maître-autel"</t>
-  </si>
-  <si>
     <t>Bronze doré</t>
   </si>
   <si>
@@ -571,9 +547,6 @@
     <t>"Pietà"</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9c/Hochaltar_von_Veit_Sto%C3%9F%2C_Marienkirche%2C_Krakau%2C_Polen.JPG/1280px-Hochaltar_von_Veit_Sto%C3%9F%2C_Marienkirche%2C_Krakau%2C_Polen.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Veit</t>
   </si>
   <si>
@@ -823,20 +796,23 @@
     <t>Terre cuite vernissée</t>
   </si>
   <si>
-    <t>di PIETRO</t>
-  </si>
-  <si>
     <t>Donato</t>
   </si>
   <si>
     <t>di NICOLO</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg/1280px-Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Benedetto_da_Maiano%2C_pulpito_di_s._croce_01.JPG/960px-Benedetto_da_Maiano%2C_pulpito_di_s._croce_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -854,6 +830,14 @@
       <i/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -894,10 +878,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -909,8 +894,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1211,10 +1198,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T31"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="88.7109375" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
@@ -1298,7 +1285,7 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1344,7 +1331,7 @@
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1390,7 +1377,7 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1436,7 +1423,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1482,7 +1469,7 @@
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="5" t="s">
         <v>58</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1528,35 +1515,35 @@
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>46</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
@@ -1574,42 +1561,40 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>78</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="I8" s="3"/>
+        <v>82</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
@@ -1621,41 +1606,41 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>85</v>
+    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
       <c r="O9" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
@@ -1667,41 +1652,41 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>95</v>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
       <c r="O10" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
@@ -1714,25 +1699,29 @@
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="5" t="s">
         <v>104</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>46</v>
@@ -1742,12 +1731,12 @@
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
       <c r="O11" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
@@ -1760,44 +1749,40 @@
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
       <c r="O12" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -1810,7 +1795,7 @@
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="5" t="s">
         <v>117</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1825,13 +1810,13 @@
         <v>120</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>123</v>
@@ -1843,7 +1828,7 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
       <c r="O13" s="3" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
@@ -1856,7 +1841,7 @@
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -1877,14 +1862,14 @@
         <v>130</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>46</v>
+        <v>131</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
@@ -1902,40 +1887,40 @@
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>133</v>
+      <c r="A15" s="5" t="s">
+        <v>134</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>139</v>
+        <v>46</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="3" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
@@ -1948,46 +1933,46 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="I16" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="3" t="s">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3" t="s">
-        <v>30</v>
+        <v>151</v>
       </c>
       <c r="T16" s="3">
         <v>1</v>
@@ -1995,45 +1980,45 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="T17" s="3">
         <v>1</v>
@@ -2041,45 +2026,45 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>166</v>
+        <v>46</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>167</v>
+        <v>47</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="3" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="T18" s="3">
         <v>1</v>
@@ -2087,39 +2072,39 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="3" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
@@ -2132,28 +2117,28 @@
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>181</v>
@@ -2165,13 +2150,13 @@
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="3" t="s">
-        <v>29</v>
+        <v>183</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3" t="s">
-        <v>30</v>
+        <v>151</v>
       </c>
       <c r="T20" s="3">
         <v>1</v>
@@ -2179,10 +2164,10 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>185</v>
@@ -2217,7 +2202,7 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3" t="s">
-        <v>159</v>
+        <v>30</v>
       </c>
       <c r="T21" s="3">
         <v>1</v>
@@ -2228,42 +2213,38 @@
         <v>193</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>50</v>
+        <v>194</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
       <c r="O22" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3" t="s">
-        <v>30</v>
+        <v>201</v>
       </c>
       <c r="T22" s="3">
         <v>1</v>
@@ -2281,31 +2262,35 @@
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="H23" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>206</v>
+        <v>46</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>207</v>
+        <v>74</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
       <c r="O23" s="3" t="s">
-        <v>209</v>
+        <v>29</v>
       </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3" t="s">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="T23" s="3">
         <v>1</v>
@@ -2313,34 +2298,32 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>46</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
@@ -2359,32 +2342,34 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
@@ -2403,34 +2388,34 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>225</v>
+        <v>97</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
@@ -2449,34 +2434,34 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="I27" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
@@ -2495,39 +2480,37 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>88</v>
+        <v>239</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
       <c r="O28" s="3" t="s">
-        <v>29</v>
+        <v>243</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
@@ -2541,26 +2524,28 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="H29" s="3" t="s">
+      <c r="I29" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
         <v>250</v>
       </c>
@@ -2571,7 +2556,7 @@
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
       <c r="O29" s="3" t="s">
-        <v>252</v>
+        <v>103</v>
       </c>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
@@ -2585,39 +2570,39 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>225</v>
+        <v>97</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>254</v>
+        <v>119</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>259</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
       <c r="O30" s="3" t="s">
-        <v>111</v>
+        <v>257</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
@@ -2629,53 +2614,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="K31" s="3"/>
-      <c r="L31" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T31" s="3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A7" r:id="rId1" xr:uid="{A02981F0-7CAC-421C-B286-4081B074BA31}"/>
+    <hyperlink ref="A20" r:id="rId2" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg/1280px-Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1ED1E423-70F8-4D6A-AD9F-8CEC3A59CCBF}"/>
+    <hyperlink ref="A2" r:id="rId3" display="https://upload.wikimedia.org/wikipedia/commons/thumb/d/db/Milano_-_Agostino_di_Duccio_%281418-1481%29_-_Allegoria_-_dal_Tempio_Malatestiano_-_Foto_Giovanni_Dall%27Orto_-_6-jan-2007_-_02.jpg/1280px-Milano_-_Agostino_di_Duccio_%281418-1481%29_-_Allegoria_-_dal_Tempio_Malatestiano_-_Foto_Giovanni_Dall%27Orto_-_6-jan-2007_-_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{243179FA-5922-4D27-8402-D36A003681A8}"/>
+    <hyperlink ref="A3" r:id="rId4" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG/1280px-Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{ADAA0411-1A0A-4E87-ADD7-3A6F6C233F3F}"/>
+    <hyperlink ref="A4" r:id="rId5" xr:uid="{B6BE7E21-9670-4328-954C-64D18FCFB87A}"/>
+    <hyperlink ref="A5" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg/1280px-Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{C11469E5-A40F-48EA-BDA9-9BC9752A5D78}"/>
+    <hyperlink ref="A6" r:id="rId7" xr:uid="{67D3FDB1-D059-4E33-9A2C-4B7EDCE09D34}"/>
+    <hyperlink ref="A8" r:id="rId8" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG/1280px-Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{C374767A-7AE4-42A2-BFC7-5307451D9668}"/>
+    <hyperlink ref="A9" r:id="rId9" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG/1280px-Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{317527F1-D630-42B2-A9E2-58C26715CABB}"/>
+    <hyperlink ref="A10" r:id="rId10" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg/1280px-David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{789194FF-DB6C-4475-9E50-5D96FC973884}"/>
+    <hyperlink ref="A11" r:id="rId11" xr:uid="{99941D0E-3DC3-44B5-9CB2-B570F2B293A9}"/>
+    <hyperlink ref="A12" r:id="rId12" display="https://upload.wikimedia.org/wikipedia/commons/thumb/d/d9/%28Venice%29_Davide_con_la_testa_di_Golia%2C_fine_secolo_XV_-_Museo_Correr.jpg/1280px-%28Venice%29_Davide_con_la_testa_di_Golia%2C_fine_secolo_XV_-_Museo_Correr.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D3407F21-9694-4D9C-8D26-FA0EB276D911}"/>
+    <hyperlink ref="A13" r:id="rId13" xr:uid="{515CC530-AB12-407E-AB5A-B6A1E37697B2}"/>
+    <hyperlink ref="A14" r:id="rId14" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{4FDE0E35-0551-43B3-A5CA-8168A50FF693}"/>
+    <hyperlink ref="A15" r:id="rId15" xr:uid="{D724919D-A8B7-4E64-8B2F-8B936CA68C5F}"/>
+    <hyperlink ref="A16" r:id="rId16" xr:uid="{9FD549A3-748A-42D8-A578-B09F744E8FD4}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69B8534-C52B-4152-9FD4-3B543FE5AECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DA329E-2F46-4E61-895C-4C25316D75EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -778,9 +778,6 @@
     <t>"Tombeau du pape Sixte IV"</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/13/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_06.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_06.JPG</t>
-  </si>
-  <si>
     <t>1525</t>
   </si>
   <si>
@@ -806,6 +803,9 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Benedetto_da_Maiano%2C_pulpito_di_s._croce_01.JPG/960px-Benedetto_da_Maiano%2C_pulpito_di_s._croce_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>ttps://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -1516,7 +1516,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>69</v>
@@ -1703,10 +1703,10 @@
         <v>104</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>259</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>105</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>175</v>
@@ -2569,8 +2569,8 @@
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>252</v>
+      <c r="A30" s="5" t="s">
+        <v>261</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>97</v>
@@ -2584,25 +2584,25 @@
         <v>99</v>
       </c>
       <c r="G30" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>46</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
       <c r="O30" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
@@ -2632,6 +2632,7 @@
     <hyperlink ref="A14" r:id="rId14" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{4FDE0E35-0551-43B3-A5CA-8168A50FF693}"/>
     <hyperlink ref="A15" r:id="rId15" xr:uid="{D724919D-A8B7-4E64-8B2F-8B936CA68C5F}"/>
     <hyperlink ref="A16" r:id="rId16" xr:uid="{9FD549A3-748A-42D8-A578-B09F744E8FD4}"/>
+    <hyperlink ref="A30" r:id="rId17" display="ttps://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EB2007DA-90C1-4C15-A4FD-EA13C6FCBC04}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>environ 1437</t>
+          <t>1437 environ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>environ 1474-1477</t>
+          <t>1474-1477 environ</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>environ 1460-1464</t>
+          <t>1460-1464 environ</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>environ 1431</t>
+          <t>1431 environ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>environ 1435</t>
+          <t>1435 environ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>environ 1374</t>
+          <t>1374 environ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>environ 1487</t>
+          <t>1487 environ</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>environ 1440</t>
+          <t>1440 environ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>environ 1386</t>
+          <t>1386 environ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>environ 1440</t>
+          <t>1440 environ</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>environ 1420</t>
+          <t>1420 environ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>environ 1470</t>
+          <t>1470 environ</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>environ 1420</t>
+          <t>1420 environ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>environ 1463</t>
+          <t>1463 environ</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>environ 1460</t>
+          <t>1460 environ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>environ 1430</t>
+          <t>1430 environ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>environ 1502</t>
+          <t>1502 environ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>environ 1435</t>
+          <t>1435 environ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>environ 1450</t>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>environ 1477-1479</t>
+          <t>1477-1479 environ</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>environ 1340</t>
+          <t>1340 environ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>environ 1447</t>
+          <t>1447 environ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
